--- a/Data/Snow Rabbit Commodities Expansion—— Playbunny Corporation - 3748316169/1.6/Snow Rabbit Commodities Expansion—— Playbunny Corporation - 3748316169.xlsx
+++ b/Data/Snow Rabbit Commodities Expansion—— Playbunny Corporation - 3748316169/1.6/Snow Rabbit Commodities Expansion—— Playbunny Corporation - 3748316169.xlsx
@@ -818,7 +818,7 @@
     <x:t>Hediff_MakeUpFancy_SR.description</x:t>
   </x:si>
   <x:si>
-    <x:t>이 스노우래빗은 화려하고 정교한 갸루 화장을 하고 있습니다. 보수적인 도원향이었다면 분명 이단아 취급을 받았을 것입니다...</x:t>
+    <x:t>이 스노우래빗은 화려하고 정교한 갸루 화장을 하고 있습니다. 보수적인 도화향이었다면 분명 이단아 취급을 받았을 것입니다...</x:t>
   </x:si>
   <x:si>
     <x:t>HediffDef+SR_PB_SmokeHigh.label</x:t>
